--- a/BeatnotePostHotCell/Jun18,2026/Fit_ResultJun18.xlsx
+++ b/BeatnotePostHotCell/Jun18,2026/Fit_ResultJun18.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostHotCell\Jun18,2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\Jun18,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F7D0DF0-DBC1-4FD5-929A-8B3B69962DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370B8D3E-A46C-4AED-9920-E389F77750A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
   <sheets>
     <sheet name="894" sheetId="2" r:id="rId1"/>
@@ -123,7 +123,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -495,9 +495,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C5617D-2BBC-4C21-ADC4-3687FEC8C6E3}">
   <dimension ref="A1:T33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -533,7 +533,7 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -559,7 +559,7 @@
       <c r="L2" s="1"/>
       <c r="T2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -584,7 +584,7 @@
       <c r="H3" s="1"/>
       <c r="T3" s="1"/>
     </row>
-    <row r="4" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -609,7 +609,7 @@
       <c r="H4" s="1"/>
       <c r="T4" s="1"/>
     </row>
-    <row r="5" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -634,7 +634,7 @@
       <c r="H5" s="1"/>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -659,7 +659,7 @@
       <c r="H6" s="1"/>
       <c r="T6" s="1"/>
     </row>
-    <row r="7" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -684,7 +684,7 @@
       <c r="H7" s="1"/>
       <c r="T7" s="1"/>
     </row>
-    <row r="8" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -709,7 +709,7 @@
       <c r="H8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -734,7 +734,7 @@
       <c r="H9" s="1"/>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -759,7 +759,7 @@
       <c r="H10" s="1"/>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -784,7 +784,7 @@
       <c r="H11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -809,7 +809,7 @@
       <c r="H12" s="1"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -834,7 +834,7 @@
       <c r="H13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
@@ -859,7 +859,7 @@
       <c r="H14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -884,7 +884,7 @@
       <c r="H15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -909,7 +909,7 @@
       <c r="H16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -919,7 +919,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -929,7 +929,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -939,7 +939,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -949,7 +949,7 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -959,7 +959,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -968,7 +968,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -977,7 +977,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -986,7 +986,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -995,7 +995,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1004,7 +1004,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1013,7 +1013,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1022,7 +1022,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1031,7 +1031,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1040,7 +1040,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1049,7 +1049,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1058,7 +1058,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1075,9 +1075,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011646E0-737D-49FA-A2CA-7848F848076B}">
   <dimension ref="A1:T40"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1113,12 +1113,12 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="1">
-        <v>0.17723933870696301</v>
+        <v>0.13803642019148099</v>
       </c>
       <c r="C2" s="1">
         <v>1.52487301637545</v>
@@ -1130,13 +1130,13 @@
         <v>-1.14231236068434E-4</v>
       </c>
       <c r="F2" s="1">
-        <v>3.23512952869079</v>
+        <v>3.1739660962472001</v>
       </c>
       <c r="G2" s="1">
-        <v>41.221898518360902</v>
+        <v>41.221899827484201</v>
       </c>
       <c r="H2" s="1">
-        <v>1.1569455113364399E-3</v>
+        <v>1.10811674271887E-3</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1148,12 +1148,12 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="1">
-        <v>0.17063092731327101</v>
+        <v>0.1328729865195</v>
       </c>
       <c r="C3" s="1">
         <v>1.5246861786958601</v>
@@ -1165,22 +1165,22 @@
         <v>-3.0478828126774801E-5</v>
       </c>
       <c r="F3" s="1">
-        <v>3.2266874901991498</v>
+        <v>3.16546778893315</v>
       </c>
       <c r="G3" s="1">
-        <v>39.298480214282499</v>
+        <v>39.295712189137298</v>
       </c>
       <c r="H3" s="1">
-        <v>7.7820168788798102E-4</v>
+        <v>6.6724460988236303E-4</v>
       </c>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="1">
-        <v>0.17490193092626999</v>
+        <v>0.136218398205117</v>
       </c>
       <c r="C4" s="1">
         <v>1.5246325996836001</v>
@@ -1192,21 +1192,21 @@
         <v>-1.33777070339282E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>3.2271412218013298</v>
+        <v>3.1659527338908702</v>
       </c>
       <c r="G4" s="1">
-        <v>39.335244145692002</v>
+        <v>39.448905486132404</v>
       </c>
       <c r="H4" s="1">
-        <v>6.5393019349282305E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7919256588024096E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>0.17702310390171999</v>
+        <v>0.13785864233595099</v>
       </c>
       <c r="C5" s="1">
         <v>1.5235439322881501</v>
@@ -1218,21 +1218,21 @@
         <v>-3.0433442885374903E-4</v>
       </c>
       <c r="F5" s="1">
-        <v>3.21743597107278</v>
+        <v>3.1562598824916801</v>
       </c>
       <c r="G5" s="1">
-        <v>41.354547403589002</v>
+        <v>41.228397532328998</v>
       </c>
       <c r="H5" s="1">
-        <v>1.1341233812691199E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.10565634371656E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>0.171948853936535</v>
+        <v>0.13392104624134801</v>
       </c>
       <c r="C6" s="1">
         <v>1.5252938371984199</v>
@@ -1244,21 +1244,21 @@
         <v>-1.3129439985086E-4</v>
       </c>
       <c r="F6" s="1">
-        <v>2.9833724655786602</v>
+        <v>2.9221760821214402</v>
       </c>
       <c r="G6" s="1">
-        <v>39.3709805160942</v>
+        <v>39.370980510094803</v>
       </c>
       <c r="H6" s="1">
-        <v>5.7857699606149297E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7857693500361297E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="1">
-        <v>0.17411860264206899</v>
+        <v>0.13552887551307799</v>
       </c>
       <c r="C7" s="1">
         <v>1.52384556726022</v>
@@ -1270,21 +1270,21 @@
         <v>-1.65403405764465E-4</v>
       </c>
       <c r="F7" s="1">
-        <v>3.2286671990468299</v>
+        <v>3.1674961685386802</v>
       </c>
       <c r="G7" s="1">
-        <v>41.358298524737997</v>
+        <v>41.348885104127397</v>
       </c>
       <c r="H7" s="1">
-        <v>1.13656199995568E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.7162314435613797E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="1">
-        <v>0.175935205113702</v>
+        <v>0.137036547539267</v>
       </c>
       <c r="C8" s="1">
         <v>1.52402562992428</v>
@@ -1296,21 +1296,21 @@
         <v>-1.13914671201913E-4</v>
       </c>
       <c r="F8" s="1">
-        <v>3.2315255396213698</v>
+        <v>3.1703227588808698</v>
       </c>
       <c r="G8" s="1">
-        <v>39.422313549752197</v>
+        <v>39.426024723009597</v>
       </c>
       <c r="H8" s="1">
-        <v>5.8088645278847801E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.0489778988364305E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="1">
-        <v>0.17427622300988699</v>
+        <v>0.135737051657839</v>
       </c>
       <c r="C9" s="1">
         <v>1.52519354835432</v>
@@ -1322,21 +1322,21 @@
         <v>-8.5704219217770704E-5</v>
       </c>
       <c r="F9" s="1">
-        <v>2.9771900837817502</v>
+        <v>2.9159888852829901</v>
       </c>
       <c r="G9" s="1">
-        <v>39.4634329000721</v>
+        <v>39.464387653215297</v>
       </c>
       <c r="H9" s="1">
-        <v>5.8116338426339995E-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7866588372459699E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="1">
-        <v>0.17224969239811899</v>
+        <v>0.13411786534959899</v>
       </c>
       <c r="C10" s="1">
         <v>1.5234272013633099</v>
@@ -1348,21 +1348,21 @@
         <v>-1.37560439919959E-4</v>
       </c>
       <c r="F10" s="1">
-        <v>3.4722379838993001</v>
+        <v>3.41103026514911</v>
       </c>
       <c r="G10" s="1">
-        <v>39.614866561726402</v>
+        <v>39.504895418644402</v>
       </c>
       <c r="H10" s="1">
-        <v>7.0893626345597802E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7980516758465196E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="1">
-        <v>0.17435257559575301</v>
+        <v>0.135674971298644</v>
       </c>
       <c r="C11" s="1">
         <v>1.52428504448478</v>
@@ -1374,21 +1374,21 @@
         <v>-2.0326599827352599E-4</v>
       </c>
       <c r="F11" s="1">
-        <v>3.2248866886165999</v>
+        <v>3.1636894238184401</v>
       </c>
       <c r="G11" s="1">
-        <v>41.460449073737898</v>
+        <v>39.637250454664503</v>
       </c>
       <c r="H11" s="1">
-        <v>5.9062269859201796E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>8.0857502111020404E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B12" s="1">
-        <v>0.171222354567128</v>
+        <v>0.13332899819484301</v>
       </c>
       <c r="C12" s="1">
         <v>1.5244947496305501</v>
@@ -1400,21 +1400,21 @@
         <v>-1.6953477753457101E-4</v>
       </c>
       <c r="F12" s="1">
-        <v>3.22038234925509</v>
+        <v>3.1591611837168401</v>
       </c>
       <c r="G12" s="1">
-        <v>39.872062402026401</v>
+        <v>40.529525606009798</v>
       </c>
       <c r="H12" s="1">
-        <v>1.15478915087406E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.5218409774860699E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B13" s="1">
-        <v>0.17230494746765301</v>
+        <v>0.13422513879040401</v>
       </c>
       <c r="C13" s="1">
         <v>1.52518163888711</v>
@@ -1426,21 +1426,21 @@
         <v>-1.4951860029242901E-4</v>
       </c>
       <c r="F13" s="1">
-        <v>2.96913758443957</v>
+        <v>2.9079381298260798</v>
       </c>
       <c r="G13" s="1">
-        <v>39.524315962115402</v>
+        <v>39.526550264601603</v>
       </c>
       <c r="H13" s="1">
-        <v>5.8603779132495801E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.8175278753615704E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="1">
-        <v>0.17976030708667101</v>
+        <v>0.14001016382505199</v>
       </c>
       <c r="C14" s="1">
         <v>1.52408865454228</v>
@@ -1452,21 +1452,21 @@
         <v>-2.3768933784083099E-4</v>
       </c>
       <c r="F14" s="1">
-        <v>3.2189334298719601</v>
+        <v>3.1577662140193898</v>
       </c>
       <c r="G14" s="1">
-        <v>41.572050123677798</v>
+        <v>41.567956475202102</v>
       </c>
       <c r="H14" s="1">
-        <v>1.15715356722524E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.13741892698977E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B15" s="1">
-        <v>0.174433801903358</v>
+        <v>0.135848256649828</v>
       </c>
       <c r="C15" s="1">
         <v>1.5235044746209601</v>
@@ -1478,21 +1478,21 @@
         <v>-1.23083871931537E-4</v>
       </c>
       <c r="F15" s="1">
-        <v>3.4804869664270499</v>
+        <v>3.4192971032666</v>
       </c>
       <c r="G15" s="1">
-        <v>39.720817791521398</v>
+        <v>39.8293720662993</v>
       </c>
       <c r="H15" s="1">
-        <v>6.7659321195702904E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7859963089952897E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B16" s="1">
-        <v>0.17714435708530099</v>
+        <v>0.13795749701744001</v>
       </c>
       <c r="C16" s="1">
         <v>1.5240152486199501</v>
@@ -1504,16 +1504,16 @@
         <v>-1.2622808017610399E-4</v>
       </c>
       <c r="F16" s="1">
-        <v>2.97790233781248</v>
+        <v>2.9167054486400699</v>
       </c>
       <c r="G16" s="1">
-        <v>41.622341512444102</v>
+        <v>41.620622940299398</v>
       </c>
       <c r="H16" s="1">
-        <v>1.15695030858436E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1.0886397549538199E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1523,7 +1523,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1533,7 +1533,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1543,7 +1543,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1553,7 +1553,7 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1563,7 +1563,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1573,7 +1573,7 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1583,7 +1583,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1593,7 +1593,7 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1603,7 +1603,7 @@
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1613,7 +1613,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1623,7 +1623,7 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1633,7 +1633,7 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1643,7 +1643,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1653,7 +1653,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1663,7 +1663,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1673,7 +1673,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1683,7 +1683,7 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1693,7 +1693,7 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1703,7 +1703,7 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1713,7 +1713,7 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1723,7 +1723,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1733,7 +1733,7 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1743,7 +1743,7 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1760,13 +1760,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF8CB368-1F4F-4C65-B86B-93EC676CB77B}">
-  <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I40"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="5" max="5" width="16.7265625" customWidth="1"/>
+    <col min="5" max="5" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>10.794234615893799</v>
       </c>
       <c r="C2" s="1">
-        <v>0.17723933870696301</v>
+        <v>0.13803642019148099</v>
       </c>
       <c r="F2">
         <v>894</v>
@@ -1793,8 +1793,9 @@
       <c r="G2">
         <v>456</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1802,7 +1803,7 @@
         <v>10.8450661689269</v>
       </c>
       <c r="C3" s="1">
-        <v>0.17063092731327101</v>
+        <v>0.1328729865195</v>
       </c>
       <c r="E3" t="s">
         <v>1</v>
@@ -1813,10 +1814,11 @@
       </c>
       <c r="G3">
         <f>AVERAGE(C2:C33)</f>
-        <v>0.17450281477696</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13589152395529275</v>
+      </c>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -1824,7 +1826,7 @@
         <v>10.7513220521733</v>
       </c>
       <c r="C4" s="1">
-        <v>0.17490193092626999</v>
+        <v>0.136218398205117</v>
       </c>
       <c r="E4" t="s">
         <v>2</v>
@@ -1835,10 +1837,11 @@
       </c>
       <c r="G4">
         <f>_xlfn.STDEV.S(C2:C33)</f>
-        <v>2.5784762064618365E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>2.0143633423445953E-3</v>
+      </c>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1846,7 +1849,7 @@
         <v>10.544390346656099</v>
       </c>
       <c r="C5" s="1">
-        <v>0.17702310390171999</v>
+        <v>0.13785864233595099</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
@@ -1857,10 +1860,11 @@
       </c>
       <c r="G5">
         <f>G4/G3/SQRT(COUNT(C2:C33))</f>
-        <v>3.8151802571142236E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>3.8273643815479332E-3</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1868,10 +1872,11 @@
         <v>10.7196028974402</v>
       </c>
       <c r="C6" s="1">
-        <v>0.171948853936535</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13392104624134801</v>
+      </c>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -1879,10 +1884,11 @@
         <v>10.753363759575</v>
       </c>
       <c r="C7" s="1">
-        <v>0.17411860264206899</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13552887551307799</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -1890,10 +1896,11 @@
         <v>10.653749196664901</v>
       </c>
       <c r="C8" s="1">
-        <v>0.175935205113702</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.137036547539267</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -1901,10 +1908,11 @@
         <v>10.8630753057798</v>
       </c>
       <c r="C9" s="1">
-        <v>0.17427622300988699</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.135737051657839</v>
+      </c>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -1912,10 +1920,11 @@
         <v>10.7208205400928</v>
       </c>
       <c r="C10" s="1">
-        <v>0.17224969239811899</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13411786534959899</v>
+      </c>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -1923,10 +1932,11 @@
         <v>10.6700806810118</v>
       </c>
       <c r="C11" s="1">
-        <v>0.17435257559575301</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.135674971298644</v>
+      </c>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -1934,10 +1944,11 @@
         <v>10.6606574449491</v>
       </c>
       <c r="C12" s="1">
-        <v>0.171222354567128</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13332899819484301</v>
+      </c>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -1945,10 +1956,11 @@
         <v>10.8131728102025</v>
       </c>
       <c r="C13" s="1">
-        <v>0.17230494746765301</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13422513879040401</v>
+      </c>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
@@ -1956,10 +1968,11 @@
         <v>10.8081420366551</v>
       </c>
       <c r="C14" s="1">
-        <v>0.17976030708667101</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.14001016382505199</v>
+      </c>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -1967,10 +1980,11 @@
         <v>10.586819027671799</v>
       </c>
       <c r="C15" s="1">
-        <v>0.174433801903358</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.135848256649828</v>
+      </c>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -1978,113 +1992,114 @@
         <v>10.7337029456849</v>
       </c>
       <c r="C16" s="1">
-        <v>0.17714435708530099</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+        <v>0.13795749701744001</v>
+      </c>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3">
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3">
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3">
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3">
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3">
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3">
       <c r="C39" s="1"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3">
       <c r="C40" s="1"/>
     </row>
   </sheetData>
